--- a/src/test/resources/MasterTestData.xlsx
+++ b/src/test/resources/MasterTestData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>testcasename</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>TC100</t>
+  </si>
+  <si>
+    <t>TC101</t>
   </si>
 </sst>
 </file>
@@ -694,7 +697,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1000,8 +1003,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="1" outlineLevelCol="7"/>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="2" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="22.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -1058,6 +1061,26 @@
         <v>1</v>
       </c>
     </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2">
+        <v>45868</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>

--- a/src/test/resources/MasterTestData.xlsx
+++ b/src/test/resources/MasterTestData.xlsx
@@ -27,15 +27,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>testcasename</t>
-  </si>
-  <si>
-    <t>username</t>
-  </si>
-  <si>
-    <t>password</t>
   </si>
   <si>
     <t>expectedTitle</t>
@@ -54,12 +48,6 @@
   </si>
   <si>
     <t>createArVoucher</t>
-  </si>
-  <si>
-    <t>aranibarman</t>
-  </si>
-  <si>
-    <t>ab</t>
   </si>
   <si>
     <t>TC100</t>
@@ -1003,19 +991,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="2" outlineLevelCol="7"/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="22.4285714285714" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="11.2190476190476" customWidth="1"/>
-    <col min="4" max="4" width="14.4380952380952" customWidth="1"/>
-    <col min="6" max="6" width="10.3333333333333" customWidth="1"/>
-    <col min="7" max="7" width="11.4285714285714" customWidth="1"/>
-    <col min="8" max="8" width="16.8571428571429" customWidth="1"/>
+    <col min="2" max="2" width="14.4380952380952" customWidth="1"/>
+    <col min="4" max="4" width="10.3333333333333" customWidth="1"/>
+    <col min="5" max="5" width="11.4285714285714" customWidth="1"/>
+    <col min="6" max="6" width="16.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1028,56 +1014,38 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="D2" s="2">
+        <v>45868</v>
+      </c>
+      <c r="E2" t="s">
         <v>7</v>
       </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" t="s">
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="2">
+        <v>45868</v>
+      </c>
+      <c r="E3" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="2">
-        <v>45868</v>
-      </c>
-      <c r="G2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="2">
-        <v>45868</v>
-      </c>
-      <c r="G3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3">
+      <c r="F3">
         <v>1</v>
       </c>
     </row>

--- a/src/test/resources/MasterTestData.xlsx
+++ b/src/test/resources/MasterTestData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>testcasename</t>
   </si>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t>TC101</t>
+  </si>
+  <si>
+    <t>createApVoucherAdvancePayment</t>
   </si>
 </sst>
 </file>
@@ -991,8 +994,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="2" outlineLevelCol="5"/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="22.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="14.4380952380952" customWidth="1"/>
@@ -1049,6 +1052,17 @@
         <v>1</v>
       </c>
     </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4">
+        <v>200</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>

--- a/src/test/resources/MasterTestData.xlsx
+++ b/src/test/resources/MasterTestData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t>testcasename</t>
   </si>
@@ -56,7 +56,19 @@
     <t>TC101</t>
   </si>
   <si>
+    <t>createApVoucherDocumentPayment</t>
+  </si>
+  <si>
     <t>createApVoucherAdvancePayment</t>
+  </si>
+  <si>
+    <t>FIN-AP-ADV-TDS-EQ</t>
+  </si>
+  <si>
+    <t>FIN-AP-ADV-TDS-PE</t>
+  </si>
+  <si>
+    <t>FIN-AP-ADV-TDS-CEPT</t>
   </si>
 </sst>
 </file>
@@ -70,13 +82,19 @@
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="180" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.75"/>
+      <color rgb="FF0A0A0A"/>
+      <name val="Courier New"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -541,140 +559,141 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -994,10 +1013,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3" outlineLevelCol="5"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="22.4285714285714" customWidth="1"/>
+    <col min="1" max="1" width="35.2857142857143" customWidth="1"/>
     <col min="2" max="2" width="14.4380952380952" customWidth="1"/>
     <col min="4" max="4" width="10.3333333333333" customWidth="1"/>
     <col min="5" max="5" width="11.4285714285714" customWidth="1"/>
@@ -1053,7 +1072,7 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" t="s">
+      <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E4" t="s">
@@ -1061,11 +1080,44 @@
       </c>
       <c r="F4">
         <v>200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait" useFirstPageNumber="1"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/src/test/resources/MasterTestData.xlsx
+++ b/src/test/resources/MasterTestData.xlsx
@@ -1079,7 +1079,7 @@
         <v>7</v>
       </c>
       <c r="F4">
-        <v>200</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:6">

--- a/src/test/resources/MasterTestData.xlsx
+++ b/src/test/resources/MasterTestData.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
   <si>
     <t>testcasename</t>
   </si>
@@ -69,6 +69,12 @@
   </si>
   <si>
     <t>FIN-AP-ADV-TDS-CEPT</t>
+  </si>
+  <si>
+    <t>createGeneralVoucher</t>
+  </si>
+  <si>
+    <t>GV_TC01</t>
   </si>
 </sst>
 </file>
@@ -1013,8 +1019,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="5"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="35.2857142857143" customWidth="1"/>
     <col min="2" max="2" width="14.4380952380952" customWidth="1"/>
@@ -1115,6 +1121,17 @@
         <v>1</v>
       </c>
     </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" useFirstPageNumber="1"/>

--- a/src/test/resources/MasterTestData.xlsx
+++ b/src/test/resources/MasterTestData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7620"/>
+    <workbookView windowWidth="20490" windowHeight="7500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
   <si>
     <t>testcasename</t>
   </si>
@@ -75,6 +75,39 @@
   </si>
   <si>
     <t>GV_TC01</t>
+  </si>
+  <si>
+    <t>revertGeneralVoucher</t>
+  </si>
+  <si>
+    <t>FIN-GV-REVERT-01</t>
+  </si>
+  <si>
+    <t>FIN-GV-REVERT-02</t>
+  </si>
+  <si>
+    <t>FIN-GV-REVERT-03</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>editGeneralVoucherHeader</t>
+  </si>
+  <si>
+    <t>GV-EDIT-001</t>
+  </si>
+  <si>
+    <t>editGeneralVoucherDetailLine</t>
+  </si>
+  <si>
+    <t>GV-EDIT-002</t>
+  </si>
+  <si>
+    <t>GV-EDIT-003</t>
+  </si>
+  <si>
+    <t>GV-EDIT-004</t>
   </si>
 </sst>
 </file>
@@ -1019,14 +1052,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="7" outlineLevelCol="5"/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="35.2857142857143" customWidth="1"/>
-    <col min="2" max="2" width="14.4380952380952" customWidth="1"/>
-    <col min="4" max="4" width="10.3333333333333" customWidth="1"/>
-    <col min="5" max="5" width="11.4285714285714" customWidth="1"/>
-    <col min="6" max="6" width="16.8571428571429" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="35.2857142857143" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" width="14.4380952380952" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" width="10.3333333333333" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" width="22.7142857142857" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" width="16.8571428571429" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1130,6 +1163,61 @@
       </c>
       <c r="F8">
         <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="F12" t="n" s="0">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="F13" t="n" s="0">
+        <v>1.0</v>
       </c>
     </row>
   </sheetData>
